--- a/public/Examination/2026年季度GMV目标模板_202610281542.xlsx
+++ b/public/Examination/2026年季度GMV目标模板_202610281542.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\入职起资料\绩效\考核目标或指标\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Peidi\peidi-pm-frontend\public\Examination\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00B43BC-3777-4C89-A7B1-C551FF58DEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="各渠道拆解到岗位" sheetId="1" r:id="rId1"/>
@@ -22,24 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">各渠道拆解到岗位!$A1:$H54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="259">
   <si>
     <t>2026年度第四季度GMV目标确认</t>
   </si>
@@ -813,21 +801,21 @@
   </si>
   <si>
     <t>OBM000017</t>
+  </si>
+  <si>
+    <t>渠道整体销售收入</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="0\.0,&quot;万&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="0\.0,&quot;万&quot;"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -928,158 +916,21 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1110,194 +961,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1372,253 +1037,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1629,7 +1052,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1662,16 +1085,13 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1680,13 +1100,10 @@
     <xf numFmtId="14" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1695,22 +1112,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1722,80 +1148,30 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2053,28 +1429,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45" customHeight="1"/>
+  <dimension ref="A1:AN71"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.8796296296296" style="10" customWidth="1"/>
+    <col min="1" max="1" width="18.875" style="10" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="11" customWidth="1"/>
-    <col min="3" max="3" width="13.3796296296296" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19.1296296296296" style="11" customWidth="1"/>
-    <col min="5" max="7" width="16.1296296296296" style="11" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="3" max="3" width="13.375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="11" customWidth="1"/>
+    <col min="5" max="7" width="16.125" style="11" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="8" max="8" width="12.5" style="11" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="9" max="9" width="18.8796296296296" style="11" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="11" customWidth="1"/>
     <col min="10" max="40" width="9" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.1" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2082,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
@@ -2111,29 +1488,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="19">
         <v>16180000</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="19">
         <v>9710000</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="19">
         <v>8090000</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="19">
         <f t="shared" ref="H3:H8" si="0">SUM(E3:G3)</f>
         <v>33980000</v>
       </c>
@@ -2141,27 +1518,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A4" s="17"/>
-      <c r="B4" s="21" t="s">
+    <row r="4" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="31"/>
+      <c r="B4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="22">
         <v>12880000</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="22">
         <v>7280000</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="22">
         <v>6050000</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
         <f t="shared" si="0"/>
         <v>26210000</v>
       </c>
@@ -2169,27 +1546,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A5" s="17"/>
-      <c r="B5" s="21" t="s">
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="31"/>
+      <c r="B5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="22">
         <v>2150000</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="22">
         <v>1420000</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="22">
         <v>1350000</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="22">
         <f t="shared" si="0"/>
         <v>4920000</v>
       </c>
@@ -2197,27 +1574,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A6" s="17"/>
-      <c r="B6" s="21" t="s">
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="31"/>
+      <c r="B6" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <v>320000</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="22">
         <v>380000</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <v>160000</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="22">
         <f t="shared" si="0"/>
         <v>860000</v>
       </c>
@@ -2226,27 +1603,27 @@
       </c>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A7" s="17"/>
-      <c r="B7" s="21" t="s">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="31"/>
+      <c r="B7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>0</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>0</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>0</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2255,27 +1632,27 @@
       </c>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A8" s="17"/>
-      <c r="B8" s="21" t="s">
+    <row r="8" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="31"/>
+      <c r="B8" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <v>750000</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="22">
         <v>500000</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>400000</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="22">
         <f t="shared" si="0"/>
         <v>1650000</v>
       </c>
@@ -2283,31 +1660,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A9" s="17"/>
-      <c r="B9" s="24" t="s">
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="31"/>
+      <c r="B9" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25">
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="23">
         <f>SUBTOTAL(9,E4:E8)</f>
         <v>16100000</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="23">
         <f>SUBTOTAL(9,F4:F8)</f>
         <v>9580000</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="23">
         <f>SUBTOTAL(9,G4:G8)</f>
         <v>7960000</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="23">
         <f>SUBTOTAL(9,H4:H8)</f>
         <v>33640000</v>
       </c>
     </row>
-    <row r="10" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="10" spans="1:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>2</v>
       </c>
@@ -2335,23 +1712,23 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20">
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19">
         <f>SUM(E11:G11)</f>
         <v>0</v>
       </c>
@@ -2359,27 +1736,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A12" s="17"/>
-      <c r="B12" s="21" t="s">
+    <row r="12" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="31"/>
+      <c r="B12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="22">
         <v>990000</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="22">
         <v>720000</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="22">
         <v>480000</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="22">
         <f>SUM(E12:G12)</f>
         <v>2190000</v>
       </c>
@@ -2387,33 +1764,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" s="8" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A13" s="17"/>
-      <c r="B13" s="24" t="s">
+    <row r="13" spans="1:10" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="31"/>
+      <c r="B13" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="25">
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="23">
         <f>SUBTOTAL(9,E12:E12)</f>
         <v>990000</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="23">
         <f>SUBTOTAL(9,F12:F12)</f>
         <v>720000</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="23">
         <f>SUBTOTAL(9,G12:G12)</f>
         <v>480000</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="23">
         <f>SUBTOTAL(9,H12:H12)</f>
         <v>2190000</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="14" spans="1:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>2</v>
       </c>
@@ -2441,29 +1818,29 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <v>4110000</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <v>3900000</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="19">
         <v>4010000</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="19">
         <f>SUM(E15:G15)</f>
         <v>12020000</v>
       </c>
@@ -2471,27 +1848,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A16" s="17"/>
-      <c r="B16" s="21" t="s">
+    <row r="16" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="31"/>
+      <c r="B16" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="22">
         <v>450000</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="22">
         <v>450000</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>400000</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <f>SUM(E16:G16)</f>
         <v>1300000</v>
       </c>
@@ -2499,27 +1876,27 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A17" s="17"/>
-      <c r="B17" s="21" t="s">
+    <row r="17" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="31"/>
+      <c r="B17" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="22">
         <v>1150000</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="22">
         <v>1200000</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="22">
         <v>1100000</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="22">
         <f>SUM(E17:G17)</f>
         <v>3450000</v>
       </c>
@@ -2527,27 +1904,27 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A18" s="17"/>
-      <c r="B18" s="21" t="s">
+    <row r="18" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="31"/>
+      <c r="B18" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="22">
         <v>250000</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="22">
         <v>250000</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="22">
         <v>240000</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="22">
         <f>SUM(E18:G18)</f>
         <v>740000</v>
       </c>
@@ -2555,33 +1932,33 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A19" s="17"/>
-      <c r="B19" s="24" t="s">
+    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="31"/>
+      <c r="B19" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="25">
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23">
         <f>SUBTOTAL(9,E16:E18)</f>
         <v>1850000</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="23">
         <f>SUBTOTAL(9,F16:F18)</f>
         <v>1900000</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="23">
         <f>SUBTOTAL(9,G16:G18)</f>
         <v>1740000</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="23">
         <f>SUBTOTAL(9,H16:H18)</f>
         <v>5490000</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="20" spans="1:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>2</v>
       </c>
@@ -2609,29 +1986,29 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A21" s="17" t="s">
+    <row r="21" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <v>2500000</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <v>500000</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="19">
         <v>1300000</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="19">
         <f>SUM(E21:G21)</f>
         <v>4300000</v>
       </c>
@@ -2639,27 +2016,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A22" s="17"/>
-      <c r="B22" s="21" t="s">
+    <row r="22" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="31"/>
+      <c r="B22" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="22">
         <v>1550000</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="22">
         <v>1200000</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="22">
         <v>1150000</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="22">
         <f>SUM(E22:G22)</f>
         <v>3900000</v>
       </c>
@@ -2667,33 +2044,33 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" s="8" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A23" s="17"/>
-      <c r="B23" s="24" t="s">
+    <row r="23" spans="1:10" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="31"/>
+      <c r="B23" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="25">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23">
         <f>SUBTOTAL(9,E22:E22)</f>
         <v>1550000</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="23">
         <f>SUBTOTAL(9,F22:F22)</f>
         <v>1200000</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="23">
         <f>SUBTOTAL(9,G22:G22)</f>
         <v>1150000</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="23">
         <f>SUBTOTAL(9,H22:H22)</f>
         <v>3900000</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="24" spans="1:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
         <v>2</v>
       </c>
@@ -2721,23 +2098,23 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A25" s="28" t="s">
+    <row r="25" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20">
+      <c r="D25" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19">
         <f>SUM(E25:G25)</f>
         <v>0</v>
       </c>
@@ -2745,21 +2122,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A26" s="29"/>
-      <c r="B26" s="21" t="s">
+    <row r="26" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="33"/>
+      <c r="B26" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23">
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22">
         <f>SUM(E26:G26)</f>
         <v>0</v>
       </c>
@@ -2767,21 +2144,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A27" s="29"/>
-      <c r="B27" s="21" t="s">
+    <row r="27" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="33"/>
+      <c r="B27" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23">
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22">
         <f>SUM(E27:G27)</f>
         <v>0</v>
       </c>
@@ -2789,21 +2166,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A28" s="29"/>
-      <c r="B28" s="21" t="s">
+    <row r="28" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="33"/>
+      <c r="B28" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23">
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22">
         <f>SUM(E28:G28)</f>
         <v>0</v>
       </c>
@@ -2811,53 +2188,59 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A29" s="29"/>
-      <c r="B29" s="21" t="s">
+    <row r="29" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="33"/>
+      <c r="B29" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-    </row>
-    <row r="30" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A30" s="29"/>
-      <c r="B30" s="21" t="s">
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22">
+        <f>SUM(E29:G29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="33"/>
+      <c r="B30" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-    </row>
-    <row r="31" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A31" s="29"/>
-      <c r="B31" s="21" t="s">
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22">
+        <f>SUM(E30:G30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="33"/>
+      <c r="B31" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23">
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22">
         <f t="shared" ref="H31:H36" si="1">SUM(E31:G31)</f>
         <v>0</v>
       </c>
@@ -2865,171 +2248,171 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A32" s="29"/>
-      <c r="B32" s="21" t="s">
+    <row r="32" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="33"/>
+      <c r="B32" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="22">
         <v>150000</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="22">
         <v>0</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="22">
         <v>0</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="22">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
-      <c r="I32" s="30" t="s">
+      <c r="I32" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="33" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A33" s="29"/>
-      <c r="B33" s="21" t="s">
+    <row r="33" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="33"/>
+      <c r="B33" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="22">
         <v>150000</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="22">
         <v>0</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="22">
         <v>0</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="22">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
-      <c r="I33" s="30" t="s">
+      <c r="I33" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="34" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A34" s="29"/>
-      <c r="B34" s="21" t="s">
+    <row r="34" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="33"/>
+      <c r="B34" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="22">
         <v>220000</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="22">
         <v>0</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="22">
         <v>0</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="22">
         <f t="shared" si="1"/>
         <v>220000</v>
       </c>
-      <c r="I34" s="30" t="s">
+      <c r="I34" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A35" s="29"/>
-      <c r="B35" s="21" t="s">
+    <row r="35" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="33"/>
+      <c r="B35" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="22">
         <v>150000</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="22">
         <v>0</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="22">
         <v>0</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="22">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
-      <c r="I35" s="30" t="s">
+      <c r="I35" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A36" s="29"/>
-      <c r="B36" s="21" t="s">
+    <row r="36" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="33"/>
+      <c r="B36" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="22">
         <v>220000</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="22">
         <v>0</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="22">
         <v>0</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="22">
         <f t="shared" si="1"/>
         <v>220000</v>
       </c>
-      <c r="I36" s="30" t="s">
+      <c r="I36" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A37" s="31"/>
-      <c r="B37" s="24" t="s">
+    <row r="37" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="34"/>
+      <c r="B37" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="25">
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="23">
         <f>SUBTOTAL(9,E26:E36)</f>
         <v>890000</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="23">
         <f>SUBTOTAL(9,F26:F36)</f>
         <v>0</v>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="23">
         <f>SUBTOTAL(9,G26:G36)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="25">
+      <c r="H37" s="23">
         <f>SUBTOTAL(9,H26:H36)</f>
         <v>890000</v>
       </c>
     </row>
-    <row r="38" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="38" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="s">
         <v>2</v>
       </c>
@@ -3057,29 +2440,29 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A39" s="28" t="s">
+    <row r="39" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="19">
         <v>1900000</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="19">
         <v>1640000</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="19">
         <v>1780000</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="19">
         <f>SUM(E39:G39)</f>
         <v>5320000</v>
       </c>
@@ -3087,27 +2470,27 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A40" s="29"/>
-      <c r="B40" s="21" t="s">
+    <row r="40" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="33"/>
+      <c r="B40" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="22">
         <v>1000000</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="22">
         <v>750000</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="22">
         <v>780000</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="22">
         <f>SUM(E40:G40)</f>
         <v>2530000</v>
       </c>
@@ -3115,27 +2498,27 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A41" s="29"/>
-      <c r="B41" s="21" t="s">
+    <row r="41" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="33"/>
+      <c r="B41" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D41" s="22" t="s">
+      <c r="D41" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="22">
         <v>800000</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="22">
         <v>600000</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="22">
         <v>600000</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="22">
         <f>SUM(E41:G41)</f>
         <v>2000000</v>
       </c>
@@ -3143,27 +2526,27 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A42" s="29"/>
-      <c r="B42" s="21" t="s">
+    <row r="42" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="33"/>
+      <c r="B42" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D42" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="22">
         <v>600000</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="22">
         <v>500000</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="22">
         <v>500000</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="22">
         <f>SUM(E42:G42)</f>
         <v>1600000</v>
       </c>
@@ -3171,31 +2554,31 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A43" s="31"/>
-      <c r="B43" s="24" t="s">
+    <row r="43" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="34"/>
+      <c r="B43" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="25">
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="23">
         <f>SUBTOTAL(9,E40:E42)</f>
         <v>2400000</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="23">
         <f>SUBTOTAL(9,F40:F42)</f>
         <v>1850000</v>
       </c>
-      <c r="G43" s="25">
+      <c r="G43" s="23">
         <f>SUBTOTAL(9,G40:G42)</f>
         <v>1880000</v>
       </c>
-      <c r="H43" s="25">
+      <c r="H43" s="23">
         <f>SUBTOTAL(9,H40:H42)</f>
         <v>6130000</v>
       </c>
     </row>
-    <row r="44" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="44" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="14" t="s">
         <v>2</v>
       </c>
@@ -3226,29 +2609,29 @@
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
     </row>
-    <row r="45" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="45" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="19">
         <v>0</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="19">
         <v>0</v>
       </c>
-      <c r="G45" s="20">
+      <c r="G45" s="19">
         <v>0</v>
       </c>
-      <c r="H45" s="20">
+      <c r="H45" s="19">
         <f>SUM(E45:G45)</f>
         <v>0</v>
       </c>
@@ -3259,21 +2642,21 @@
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
     </row>
-    <row r="46" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="46" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="33"/>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23">
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22">
         <f>SUM(E46:G46)</f>
         <v>0</v>
       </c>
@@ -3281,21 +2664,21 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A47" s="34"/>
-      <c r="B47" s="21" t="s">
+    <row r="47" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35"/>
+      <c r="B47" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="23">
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22">
         <f>SUM(E47:G47)</f>
         <v>0</v>
       </c>
@@ -3303,31 +2686,31 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A48" s="35"/>
-      <c r="B48" s="24" t="s">
+    <row r="48" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="36"/>
+      <c r="B48" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="25">
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="23">
         <f>SUBTOTAL(9,E46:E47)</f>
         <v>0</v>
       </c>
-      <c r="F48" s="25">
+      <c r="F48" s="23">
         <f>SUBTOTAL(9,F46:F47)</f>
         <v>0</v>
       </c>
-      <c r="G48" s="25">
+      <c r="G48" s="23">
         <f>SUBTOTAL(9,G46:G47)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="25">
+      <c r="H48" s="23">
         <f>SUBTOTAL(9,H46:H47)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="49" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
         <v>2</v>
       </c>
@@ -3358,29 +2741,29 @@
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
     </row>
-    <row r="50" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A50" s="17" t="s">
+    <row r="50" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C50" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="19">
         <v>1590000</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="19">
         <v>1390000</v>
       </c>
-      <c r="G50" s="20">
+      <c r="G50" s="19">
         <v>1490000</v>
       </c>
-      <c r="H50" s="20">
+      <c r="H50" s="19">
         <f t="shared" ref="H50:H55" si="2">SUM(E50:G50)</f>
         <v>4470000</v>
       </c>
@@ -3391,27 +2774,27 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
     </row>
-    <row r="51" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A51" s="17"/>
-      <c r="B51" s="36" t="s">
+    <row r="51" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="31"/>
+      <c r="B51" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="C51" s="37" t="s">
+      <c r="C51" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D51" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="22">
         <v>330000</v>
       </c>
-      <c r="F51" s="23">
+      <c r="F51" s="22">
         <v>280000</v>
       </c>
-      <c r="G51" s="23">
+      <c r="G51" s="22">
         <v>330000</v>
       </c>
-      <c r="H51" s="23">
+      <c r="H51" s="22">
         <f t="shared" si="2"/>
         <v>940000</v>
       </c>
@@ -3419,51 +2802,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="52" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A52" s="17"/>
+    <row r="52" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="31"/>
       <c r="B52" s="38"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="22" t="s">
+      <c r="C52" s="40"/>
+      <c r="D52" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="E52" s="23">
+      <c r="E52" s="22">
         <v>150000</v>
       </c>
-      <c r="F52" s="23">
+      <c r="F52" s="22">
         <v>150000</v>
       </c>
-      <c r="G52" s="23">
+      <c r="G52" s="22">
         <v>150000</v>
       </c>
-      <c r="H52" s="23">
+      <c r="H52" s="22">
         <f t="shared" si="2"/>
         <v>450000</v>
       </c>
-      <c r="I52" s="30" t="s">
+      <c r="I52" s="26" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A53" s="17"/>
-      <c r="B53" s="36" t="s">
+    <row r="53" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="31"/>
+      <c r="B53" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="C53" s="37" t="s">
+      <c r="C53" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="E53" s="23">
+      <c r="E53" s="22">
         <v>330000</v>
       </c>
-      <c r="F53" s="23">
+      <c r="F53" s="22">
         <v>320000</v>
       </c>
-      <c r="G53" s="23">
+      <c r="G53" s="22">
         <v>350000</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="22">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
@@ -3471,51 +2854,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A54" s="17"/>
+    <row r="54" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="31"/>
       <c r="B54" s="38"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="22" t="s">
+      <c r="C54" s="40"/>
+      <c r="D54" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="22">
         <v>120000</v>
       </c>
-      <c r="F54" s="23">
+      <c r="F54" s="22">
         <v>100000</v>
       </c>
-      <c r="G54" s="23">
+      <c r="G54" s="22">
         <v>100000</v>
       </c>
-      <c r="H54" s="23">
+      <c r="H54" s="22">
         <f t="shared" si="2"/>
         <v>320000</v>
       </c>
-      <c r="I54" s="30" t="s">
+      <c r="I54" s="26" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="55" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A55" s="17"/>
-      <c r="B55" s="21" t="s">
+    <row r="55" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="31"/>
+      <c r="B55" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E55" s="23">
+      <c r="E55" s="22">
         <v>80000</v>
       </c>
-      <c r="F55" s="23">
+      <c r="F55" s="22">
         <v>70000</v>
       </c>
-      <c r="G55" s="23">
+      <c r="G55" s="22">
         <v>80000</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="22">
         <f t="shared" si="2"/>
         <v>230000</v>
       </c>
@@ -3523,31 +2906,31 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A56" s="17"/>
-      <c r="B56" s="24" t="s">
+    <row r="56" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="31"/>
+      <c r="B56" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25">
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="23">
         <f>SUBTOTAL(9,E51:E55)</f>
         <v>1010000</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="23">
         <f>SUBTOTAL(9,F51:F55)</f>
         <v>920000</v>
       </c>
-      <c r="G56" s="25">
+      <c r="G56" s="23">
         <f>SUBTOTAL(9,G51:G55)</f>
         <v>1010000</v>
       </c>
-      <c r="H56" s="25">
+      <c r="H56" s="23">
         <f>SUBTOTAL(9,H51:H55)</f>
         <v>2940000</v>
       </c>
     </row>
-    <row r="57" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="14" t="s">
         <v>2</v>
       </c>
@@ -3578,29 +2961,29 @@
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
     </row>
-    <row r="58" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A58" s="17" t="s">
+    <row r="58" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="C58" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="D58" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="19">
         <v>4070000</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="19">
         <v>3700000</v>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="19">
         <v>3790000</v>
       </c>
-      <c r="H58" s="20">
+      <c r="H58" s="19">
         <f>SUM(E58:G58)</f>
         <v>11560000</v>
       </c>
@@ -3609,27 +2992,27 @@
       </c>
       <c r="M58" s="5"/>
     </row>
-    <row r="59" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A59" s="17"/>
-      <c r="B59" s="21" t="s">
+    <row r="59" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="31"/>
+      <c r="B59" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E59" s="23">
+      <c r="E59" s="22">
         <v>1350000</v>
       </c>
-      <c r="F59" s="23">
+      <c r="F59" s="22">
         <v>1250000</v>
       </c>
-      <c r="G59" s="23">
+      <c r="G59" s="22">
         <v>1050000</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="22">
         <f>SUM(E59:G59)</f>
         <v>3650000</v>
       </c>
@@ -3639,27 +3022,27 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A60" s="17"/>
-      <c r="B60" s="21" t="s">
+    <row r="60" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="31"/>
+      <c r="B60" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="22">
         <v>1100000</v>
       </c>
-      <c r="F60" s="23">
+      <c r="F60" s="22">
         <v>90</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="22">
         <v>90</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="22">
         <f>SUM(E60:G60)</f>
         <v>1100180</v>
       </c>
@@ -3667,31 +3050,31 @@
         <v>101</v>
       </c>
     </row>
-    <row r="61" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A61" s="17"/>
-      <c r="B61" s="24" t="s">
+    <row r="61" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="31"/>
+      <c r="B61" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="25">
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="23">
         <f>SUBTOTAL(9,E59:E60)</f>
         <v>2450000</v>
       </c>
-      <c r="F61" s="25">
+      <c r="F61" s="23">
         <f>SUBTOTAL(9,F59:F60)</f>
         <v>1250090</v>
       </c>
-      <c r="G61" s="25">
+      <c r="G61" s="23">
         <f>SUBTOTAL(9,G59:G60)</f>
         <v>1050090</v>
       </c>
-      <c r="H61" s="25">
+      <c r="H61" s="23">
         <f>SUBTOTAL(9,H59:H60)</f>
         <v>4750180</v>
       </c>
     </row>
-    <row r="62" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="14" t="s">
         <v>2</v>
       </c>
@@ -3722,29 +3105,29 @@
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
     </row>
-    <row r="63" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A63" s="17" t="s">
+    <row r="63" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="20">
+      <c r="E63" s="19">
         <v>11910000</v>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="19">
         <v>13080000</v>
       </c>
-      <c r="G63" s="20">
+      <c r="G63" s="19">
         <v>13890000</v>
       </c>
-      <c r="H63" s="20">
+      <c r="H63" s="19">
         <f>SUM(E63:G63)</f>
         <v>38880000</v>
       </c>
@@ -3753,27 +3136,27 @@
       </c>
       <c r="M63" s="5"/>
     </row>
-    <row r="64" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A64" s="17"/>
-      <c r="B64" s="21" t="s">
+    <row r="64" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="31"/>
+      <c r="B64" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="C64" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="22">
         <v>150000</v>
       </c>
-      <c r="F64" s="23">
+      <c r="F64" s="22">
         <v>120000</v>
       </c>
-      <c r="G64" s="23">
+      <c r="G64" s="22">
         <v>150000</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="22">
         <f>SUM(E64:G64)</f>
         <v>420000</v>
       </c>
@@ -3783,35 +3166,35 @@
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
     </row>
-    <row r="65" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
-      <c r="A65" s="17"/>
-      <c r="B65" s="24" t="s">
+    <row r="65" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="31"/>
+      <c r="B65" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="25">
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="23">
         <f>SUBTOTAL(9,E64)</f>
         <v>150000</v>
       </c>
-      <c r="F65" s="25">
+      <c r="F65" s="23">
         <f>SUBTOTAL(9,F64)</f>
         <v>120000</v>
       </c>
-      <c r="G65" s="25">
+      <c r="G65" s="23">
         <f>SUBTOTAL(9,G64)</f>
         <v>150000</v>
       </c>
-      <c r="H65" s="25">
+      <c r="H65" s="23">
         <f>SUBTOTAL(9,H64)</f>
         <v>420000</v>
       </c>
     </row>
-    <row r="66" ht="20.1" customHeight="1" spans="1:13">
-      <c r="G66" s="20" t="s">
+    <row r="66" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G66" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="H66" s="20">
+      <c r="H66" s="19">
         <f>H63+H50+H45+H39+H15+H3+H21+H58+H11+H25</f>
         <v>110530000</v>
       </c>
@@ -3821,11 +3204,11 @@
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
     </row>
-    <row r="67" ht="20.1" customHeight="1" spans="1:13">
-      <c r="G67" s="20" t="s">
+    <row r="67" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G67" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="19">
         <f>H9+H19+H23+H37+H48+H56+H65+H61+H13+H43</f>
         <v>60350180</v>
       </c>
@@ -3834,100 +3217,98 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" s="8" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+    <row r="68" spans="1:13" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
       <c r="E68" s="11"/>
       <c r="F68" s="11"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="40"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
       <c r="K68" s="11"/>
       <c r="L68" s="11"/>
       <c r="M68" s="11"/>
     </row>
-    <row r="69" s="9" customFormat="1" ht="51.6" customHeight="1" spans="1:13">
-      <c r="A69" s="41" t="s">
+    <row r="69" spans="1:13" s="9" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B69" s="42"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
       <c r="K69" s="11"/>
       <c r="L69" s="11"/>
       <c r="M69" s="8"/>
     </row>
-    <row r="70" customHeight="1" spans="1:13">
+    <row r="70" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
       <c r="M70" s="9"/>
     </row>
-    <row r="71" customHeight="1" spans="1:13">
+    <row r="71" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
       <c r="K71" s="9"/>
       <c r="L71" s="9"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:J71" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A2:J71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="24">
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A50:A56"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A25:A37"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="C53:C54"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A25:A37"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A50:A56"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="C53:C54"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.298611111111111" footer="0.298611111111111"/>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.29861111111111099" footer="0.29861111111111099"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" useFirstPageNumber="1"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultColWidth="7.37962962962963" defaultRowHeight="14.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="7.375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="19.1296296296296" style="1" customWidth="1"/>
-    <col min="5" max="5" width="31.6296296296296" style="1" customWidth="1"/>
-    <col min="6" max="9" width="19.1296296296296" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="7.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="4" width="19.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="31.625" style="1" customWidth="1"/>
+    <col min="6" max="9" width="19.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="7.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -3956,7 +3337,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:9">
+    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>121</v>
       </c>
@@ -3983,7 +3364,7 @@
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>128</v>
       </c>
@@ -4010,7 +3391,7 @@
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:9">
+    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>133</v>
       </c>
@@ -4037,7 +3418,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:9">
+    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>138</v>
       </c>
@@ -4064,7 +3445,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:9">
+    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>141</v>
       </c>
@@ -4091,7 +3472,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>145</v>
       </c>
@@ -4118,7 +3499,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:9">
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>150</v>
       </c>
@@ -4145,7 +3526,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:9">
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>153</v>
       </c>
@@ -4172,7 +3553,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:9">
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>156</v>
       </c>
@@ -4199,7 +3580,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:9">
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>160</v>
       </c>
@@ -4226,7 +3607,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:9">
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>164</v>
       </c>
@@ -4253,7 +3634,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:9">
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>167</v>
       </c>
@@ -4280,7 +3661,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:9">
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>170</v>
       </c>
@@ -4307,7 +3688,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:9">
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>174</v>
       </c>
@@ -4334,7 +3715,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:9">
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>178</v>
       </c>
@@ -4361,7 +3742,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:9">
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>181</v>
       </c>
@@ -4388,7 +3769,7 @@
       </c>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:9">
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>184</v>
       </c>
@@ -4415,7 +3796,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:9">
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>187</v>
       </c>
@@ -4442,7 +3823,7 @@
       </c>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:9">
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>190</v>
       </c>
@@ -4469,7 +3850,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:9">
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>194</v>
       </c>
@@ -4496,7 +3877,7 @@
       </c>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:9">
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>197</v>
       </c>
@@ -4523,7 +3904,7 @@
       </c>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:9">
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>200</v>
       </c>
@@ -4550,7 +3931,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:9">
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>203</v>
       </c>
@@ -4577,7 +3958,7 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:9">
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>207</v>
       </c>
@@ -4604,7 +3985,7 @@
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:9">
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>210</v>
       </c>
@@ -4631,7 +4012,7 @@
       </c>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:9">
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>213</v>
       </c>
@@ -4658,7 +4039,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="1:9">
+    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -4685,7 +4066,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="1:9">
+    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>220</v>
       </c>
@@ -4712,7 +4093,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="1:9">
+    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>222</v>
       </c>
@@ -4739,7 +4120,7 @@
       </c>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="1:9">
+    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>225</v>
       </c>
@@ -4766,7 +4147,7 @@
       </c>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="1:9">
+    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>227</v>
       </c>
@@ -4793,7 +4174,7 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="1:9">
+    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>231</v>
       </c>
@@ -4820,7 +4201,7 @@
       </c>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="1:9">
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>234</v>
       </c>
@@ -4847,7 +4228,7 @@
       </c>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="1:9">
+    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>238</v>
       </c>
@@ -4874,7 +4255,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="1:9">
+    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>241</v>
       </c>
@@ -4901,7 +4282,7 @@
       </c>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="1:9">
+    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>243</v>
       </c>
@@ -4928,7 +4309,7 @@
       </c>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="1:9">
+    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>246</v>
       </c>
@@ -4955,7 +4336,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="1:9">
+    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>248</v>
       </c>
@@ -4982,7 +4363,7 @@
       </c>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="1:9">
+    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>250</v>
       </c>
@@ -5009,7 +4390,7 @@
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" ht="20.1" customHeight="1" spans="1:9">
+    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>253</v>
       </c>
@@ -5036,7 +4417,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="1:9">
+    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>256</v>
       </c>
@@ -5064,10 +4445,8 @@
       <c r="I42" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I42" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:I42" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>